--- a/artfynd/A 30409-2025 artfynd.xlsx
+++ b/artfynd/A 30409-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68116595</v>
+        <v>68116597</v>
       </c>
       <c r="B2" t="n">
-        <v>87429</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5581</v>
+        <v>805</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulfotsskölding</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pluteus romellii</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Britzelm.) Sacc.</t>
+          <t>(Fr.) P.Kumm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518376.2120679774</v>
+        <v>518381</v>
       </c>
       <c r="R2" t="n">
-        <v>6561827.041666925</v>
+        <v>6561849</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2017-10-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68116597</v>
+        <v>111919820</v>
       </c>
       <c r="B3" t="n">
-        <v>86157</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,7 +787,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -823,17 +803,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>S om Karlsholm, Nrk</t>
+          <t>Östra Gården, SV om, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518381.2375721522</v>
+        <v>518422</v>
       </c>
       <c r="R3" t="n">
-        <v>6561849.093971279</v>
+        <v>6561843</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-10-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-10-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,53 +853,53 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>hasselrik lövskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Herbert Kaufmann</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111919820</v>
+        <v>111919846</v>
       </c>
       <c r="B4" t="n">
-        <v>86318</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>805</v>
+        <v>3884</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Scharlakansvaxskivling</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrocybe punicea</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518422</v>
+        <v>518372</v>
       </c>
       <c r="R4" t="n">
-        <v>6561843</v>
+        <v>6561896</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,6 +973,103 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>68116595</v>
+      </c>
+      <c r="B5" t="n">
+        <v>89902</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5581</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulfotsskölding</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pluteus romellii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Britzelm.) Sacc.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>S om Karlsholm, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>518376</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6561827</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gällersta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-10-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-10-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30409-2025 artfynd.xlsx
+++ b/artfynd/A 30409-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68116597</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111919820</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111919846</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,8 +1090,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68116595</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>